--- a/02-Excel/Popular Excel Functions.xlsx
+++ b/02-Excel/Popular Excel Functions.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27531"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/579481080490e445/Documents/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\0-AI\DataAnalyst\DataAnalyst_Portfolio\02-Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="176" documentId="8_{9C4A84AA-A10A-45A0-8BFB-153DCBCC707A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C9769923-F013-4DC5-8586-F4A226F8492E}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="14620" activeTab="4" xr2:uid="{194D158C-C4D1-45A9-AB97-E05CA898B1C7}"/>
+    <workbookView xWindow="1515" yWindow="1515" windowWidth="21750" windowHeight="13890" activeTab="2" xr2:uid="{194D158C-C4D1-45A9-AB97-E05CA898B1C7}"/>
   </bookViews>
   <sheets>
     <sheet name="DateDif" sheetId="5" r:id="rId1"/>
@@ -218,7 +218,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Aptos Narrow"/>
+      <name val="Arial"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -599,9 +599,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BDAD7428-F1A8-4058-B23F-EE095F65EBB9}">
   <dimension ref="A1:F6"/>
-  <sheetFormatPr defaultColWidth="21.6328125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="21.625" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -621,7 +621,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -644,7 +644,7 @@
         <v>4072</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -667,7 +667,7 @@
         <v>1912</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -690,7 +690,7 @@
         <v>3731</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>6</v>
       </c>
@@ -713,7 +713,7 @@
         <v>2326</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>7</v>
       </c>
@@ -744,12 +744,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{22F7ECBD-6891-4F65-84A2-153FDF795B76}">
   <dimension ref="A1:E6"/>
-  <sheetFormatPr defaultColWidth="38.08984375" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="38.125" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="5" width="23.1796875" customWidth="1"/>
+    <col min="2" max="5" width="23.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>30</v>
       </c>
@@ -766,7 +766,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>34</v>
       </c>
@@ -783,7 +783,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>35</v>
       </c>
@@ -800,7 +800,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>36</v>
       </c>
@@ -817,7 +817,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>37</v>
       </c>
@@ -834,7 +834,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>38</v>
       </c>
@@ -859,9 +859,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{62A034C3-C52C-4913-814C-951B6EB5148A}">
   <dimension ref="A1:D7"/>
-  <sheetFormatPr defaultColWidth="18.36328125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="18.375" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -872,7 +872,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -888,7 +888,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -904,7 +904,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -920,7 +920,7 @@
         <v>700</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>6</v>
       </c>
@@ -936,7 +936,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>7</v>
       </c>
@@ -952,7 +952,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
       <c r="B7">
         <f>COUNTIF(B2:B6, "&gt;5000")</f>
         <v>3</v>
@@ -966,9 +966,9 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27B93885-3E45-4930-934C-8776E649571B}">
   <dimension ref="A1:B8"/>
-  <sheetFormatPr defaultColWidth="20" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="20" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>23</v>
       </c>
@@ -976,7 +976,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>25</v>
       </c>
@@ -985,7 +985,7 @@
         <v>PROD_001</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>26</v>
       </c>
@@ -994,7 +994,7 @@
         <v>PROD_002</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>27</v>
       </c>
@@ -1003,7 +1003,7 @@
         <v>ITEM_123</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>28</v>
       </c>
@@ -1012,7 +1012,7 @@
         <v>ITEM_456</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>29</v>
       </c>
@@ -1021,7 +1021,7 @@
         <v>SKU_789</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>55</v>
       </c>
@@ -1038,9 +1038,9 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7BB9A601-D5C4-4DEE-B29D-F127D273EF3F}">
   <dimension ref="A1:C18"/>
-  <sheetFormatPr defaultColWidth="22.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="22.75" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>17</v>
       </c>
@@ -1051,7 +1051,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1063,7 +1063,7 @@
         <v>Haverbrook</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -1071,11 +1071,11 @@
         <v>12</v>
       </c>
       <c r="C3" t="str">
-        <f t="shared" ref="C3:C6" si="0">_xlfn.XLOOKUP(B3,$A$14:$A$18,$B$14:$B$18)</f>
+        <f t="shared" ref="C3:C5" si="0">_xlfn.XLOOKUP(B3,$A$14:$A$18,$B$14:$B$18)</f>
         <v>Haverbrook</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -1087,7 +1087,7 @@
         <v>Greene</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>6</v>
       </c>
@@ -1099,7 +1099,7 @@
         <v>Greene</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>7</v>
       </c>
@@ -1111,7 +1111,7 @@
         <v>Greene</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1119,7 +1119,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>13</v>
       </c>
@@ -1127,7 +1127,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>14</v>
       </c>
@@ -1135,7 +1135,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>15</v>
       </c>
@@ -1143,7 +1143,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>10</v>
       </c>
@@ -1151,7 +1151,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>12</v>
       </c>
